--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.48690250208051</v>
+        <v>3.654121656588083</v>
       </c>
       <c r="D2" t="n">
-        <v>22.60691389214864</v>
+        <v>3.673623507474155</v>
       </c>
       <c r="E2" t="n">
-        <v>12.02279495529615</v>
+        <v>1.953704180235624</v>
       </c>
       <c r="F2" t="n">
-        <v>12.84733620303924</v>
+        <v>2.087692132993877</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.7763665935508</v>
+        <v>8.413659571452007</v>
       </c>
       <c r="D3" t="n">
-        <v>57.44845806028915</v>
+        <v>9.335374434796988</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02279495529615</v>
+        <v>1.953704180235624</v>
       </c>
       <c r="F3" t="n">
-        <v>12.84733620303924</v>
+        <v>2.087692132993877</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.03349876583227</v>
+        <v>5.855443549447744</v>
       </c>
       <c r="D4" t="n">
-        <v>47.12696516035384</v>
+        <v>7.658131838557499</v>
       </c>
       <c r="E4" t="n">
-        <v>12.02279495529615</v>
+        <v>1.953704180235624</v>
       </c>
       <c r="F4" t="n">
-        <v>12.84733620303924</v>
+        <v>2.087692132993877</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.6967060825549</v>
+        <v>3.688214738415172</v>
       </c>
       <c r="D5" t="n">
-        <v>47.51267294410222</v>
+        <v>7.720809353416611</v>
       </c>
       <c r="E5" t="n">
-        <v>12.02279495529615</v>
+        <v>1.953704180235624</v>
       </c>
       <c r="F5" t="n">
-        <v>12.84733620303924</v>
+        <v>2.087692132993877</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
